--- a/DXCM_Model.xlsx
+++ b/DXCM_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Health Care\MedTech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E594A8D9-38C6-4D43-B94E-002CC05FAB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B42CB34-1519-458B-8724-601805DE6857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -4704,10 +4704,10 @@
     <t>Financial Stmts. Notes/Observations</t>
   </si>
   <si>
-    <t>10/31/2025</t>
-  </si>
-  <si>
     <t>Q3'25</t>
+  </si>
+  <si>
+    <t>1/10/2026</t>
   </si>
 </sst>
 </file>
@@ -12285,10 +12285,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="46">
-        <v>58.23</v>
+        <v>67.55</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -12299,7 +12299,7 @@
         <v>390</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="C5" s="47">
         <f>C3*C4</f>
-        <v>22709.699999999997</v>
+        <v>26344.5</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -12320,7 +12320,7 @@
         <v>3322.1000000000004</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -12332,7 +12332,7 @@
         <v>2446.8000000000002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="C8" s="47">
         <f>C5-C6+C7</f>
-        <v>21834.399999999998</v>
+        <v>25469.200000000001</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15">
@@ -16907,11 +16907,11 @@
       </c>
       <c r="CG29" s="55">
         <f>CG26*CG40</f>
-        <v>616.17004750000001</v>
+        <v>606.90433250000001</v>
       </c>
       <c r="CH29" s="55">
         <f t="shared" ref="CH29:CP29" si="54">CH26*CH40</f>
-        <v>696.999069975</v>
+        <v>691.63753866749994</v>
       </c>
       <c r="CI29" s="55">
         <f t="shared" si="54"/>
@@ -17185,43 +17185,43 @@
       </c>
       <c r="CG30" s="55">
         <f>CG26*CG41</f>
-        <v>1324.997245</v>
+        <v>1320.3643875</v>
       </c>
       <c r="CH30" s="55">
         <f t="shared" ref="CH30:CP30" si="55">CH26*CH41</f>
-        <v>1517.3133600224996</v>
+        <v>1474.4211095625001</v>
       </c>
       <c r="CI30" s="55">
         <f t="shared" si="55"/>
-        <v>1729.0148946367499</v>
+        <v>1673.4394158805685</v>
       </c>
       <c r="CJ30" s="55">
         <f t="shared" si="55"/>
-        <v>1949.6099366006715</v>
+        <v>1893.0995036557244</v>
       </c>
       <c r="CK30" s="55">
         <f t="shared" si="55"/>
-        <v>2185.2813453735916</v>
+        <v>2129.248490364012</v>
       </c>
       <c r="CL30" s="55">
         <f t="shared" si="55"/>
-        <v>2430.2659547824055</v>
+        <v>2385.2610296938424</v>
       </c>
       <c r="CM30" s="55">
         <f t="shared" si="55"/>
-        <v>2695.66752389569</v>
+        <v>2655.4336802554558</v>
       </c>
       <c r="CN30" s="55">
         <f t="shared" si="55"/>
-        <v>2972.1017532737437</v>
+        <v>2938.5818086879494</v>
       </c>
       <c r="CO30" s="55">
         <f t="shared" si="55"/>
-        <v>3269.3370641293805</v>
+        <v>3232.3257011392366</v>
       </c>
       <c r="CP30" s="55">
         <f t="shared" si="55"/>
-        <v>3577.2451069880367</v>
+        <v>3536.5945944086275</v>
       </c>
     </row>
     <row r="31" spans="2:146" ht="14.25" customHeight="1">
@@ -17522,43 +17522,43 @@
       </c>
       <c r="CG31" s="55">
         <f>CG28-SUM(CG29:CG30)</f>
-        <v>857.07863750000001</v>
+        <v>870.97721000000001</v>
       </c>
       <c r="CH31" s="55">
         <f t="shared" ref="CH31:CP31" si="114">CH28-SUM(CH29:CH30)</f>
-        <v>1056.2216675774998</v>
+        <v>1104.4754493449996</v>
       </c>
       <c r="CI31" s="55">
         <f t="shared" si="114"/>
-        <v>1290.5861177824304</v>
+        <v>1346.1615965386118</v>
       </c>
       <c r="CJ31" s="55">
         <f t="shared" si="114"/>
-        <v>1554.0369059860423</v>
+        <v>1610.5473389309896</v>
       </c>
       <c r="CK31" s="55">
         <f t="shared" si="114"/>
-        <v>1817.0654410249276</v>
+        <v>1873.0982960345073</v>
       </c>
       <c r="CL31" s="55">
         <f t="shared" si="114"/>
-        <v>2101.7300016358931</v>
+        <v>2146.7349267244563</v>
       </c>
       <c r="CM31" s="55">
         <f t="shared" si="114"/>
-        <v>2403.9721575039921</v>
+        <v>2444.2060011442263</v>
       </c>
       <c r="CN31" s="55">
         <f t="shared" si="114"/>
-        <v>2759.8087708970479</v>
+        <v>2793.3287154828422</v>
       </c>
       <c r="CO31" s="55">
         <f t="shared" si="114"/>
-        <v>3133.6287331655194</v>
+        <v>3170.6400961556628</v>
       </c>
       <c r="CP31" s="55">
         <f t="shared" si="114"/>
-        <v>3604.3454487076433</v>
+        <v>3644.9959612870525</v>
       </c>
     </row>
     <row r="32" spans="2:146" ht="14.25" customHeight="1">
@@ -17800,43 +17800,43 @@
       </c>
       <c r="CG32" s="55">
         <f>CF32*(1+$CP$48)</f>
-        <v>126.54900000000001</v>
+        <v>128.07500000000002</v>
       </c>
       <c r="CH32" s="55">
         <f t="shared" ref="CH32:CP32" si="115">CG32*(1+$CP$48)</f>
-        <v>146.92338900000001</v>
+        <v>150.48812500000003</v>
       </c>
       <c r="CI32" s="55">
         <f t="shared" si="115"/>
-        <v>170.57805462900001</v>
+        <v>176.82354687500003</v>
       </c>
       <c r="CJ32" s="55">
         <f t="shared" si="115"/>
-        <v>198.04112142426902</v>
+        <v>207.76766757812504</v>
       </c>
       <c r="CK32" s="55">
         <f t="shared" si="115"/>
-        <v>229.92574197357635</v>
+        <v>244.12700940429693</v>
       </c>
       <c r="CL32" s="55">
         <f t="shared" si="115"/>
-        <v>266.94378643132217</v>
+        <v>286.84923605004889</v>
       </c>
       <c r="CM32" s="55">
         <f t="shared" si="115"/>
-        <v>309.92173604676503</v>
+        <v>337.04785235880746</v>
       </c>
       <c r="CN32" s="55">
         <f t="shared" si="115"/>
-        <v>359.81913555029422</v>
+        <v>396.0312265215988</v>
       </c>
       <c r="CO32" s="55">
         <f t="shared" si="115"/>
-        <v>417.75001637389158</v>
+        <v>465.33669116287859</v>
       </c>
       <c r="CP32" s="55">
         <f t="shared" si="115"/>
-        <v>485.00776901008817</v>
+        <v>546.77061211638238</v>
       </c>
     </row>
     <row r="33" spans="2:146" ht="14.25" customHeight="1">
@@ -18137,43 +18137,43 @@
       </c>
       <c r="CG33" s="55">
         <f>CG31+CG32</f>
-        <v>983.62763749999999</v>
+        <v>999.05221000000006</v>
       </c>
       <c r="CH33" s="55">
         <f t="shared" ref="CH33:CP33" si="174">CH31+CH32</f>
-        <v>1203.1450565774999</v>
+        <v>1254.9635743449996</v>
       </c>
       <c r="CI33" s="55">
         <f t="shared" si="174"/>
-        <v>1461.1641724114304</v>
+        <v>1522.9851434136117</v>
       </c>
       <c r="CJ33" s="55">
         <f t="shared" si="174"/>
-        <v>1752.0780274103113</v>
+        <v>1818.3150065091145</v>
       </c>
       <c r="CK33" s="55">
         <f t="shared" si="174"/>
-        <v>2046.991182998504</v>
+        <v>2117.2253054388043</v>
       </c>
       <c r="CL33" s="55">
         <f t="shared" si="174"/>
-        <v>2368.6737880672154</v>
+        <v>2433.5841627745053</v>
       </c>
       <c r="CM33" s="55">
         <f t="shared" si="174"/>
-        <v>2713.8938935507572</v>
+        <v>2781.253853503034</v>
       </c>
       <c r="CN33" s="55">
         <f t="shared" si="174"/>
-        <v>3119.627906447342</v>
+        <v>3189.3599420044411</v>
       </c>
       <c r="CO33" s="55">
         <f t="shared" si="174"/>
-        <v>3551.3787495394108</v>
+        <v>3635.9767873185415</v>
       </c>
       <c r="CP33" s="55">
         <f t="shared" si="174"/>
-        <v>4089.3532177177312</v>
+        <v>4191.7665734034344</v>
       </c>
     </row>
     <row r="34" spans="2:146" ht="14.25" customHeight="1">
@@ -18415,43 +18415,43 @@
       </c>
       <c r="CG34" s="55">
         <f>CG33*CG43</f>
-        <v>204.10273478124998</v>
+        <v>207.30333357500001</v>
       </c>
       <c r="CH34" s="55">
         <f t="shared" ref="CH34:CP34" si="175">CH33*CH43</f>
-        <v>228.59756074972498</v>
+        <v>238.44307912554993</v>
       </c>
       <c r="CI34" s="55">
         <f t="shared" si="175"/>
-        <v>277.62119275817179</v>
+        <v>274.13732581445009</v>
       </c>
       <c r="CJ34" s="55">
         <f t="shared" si="175"/>
-        <v>332.89482520795917</v>
+        <v>327.29670117164062</v>
       </c>
       <c r="CK34" s="55">
         <f t="shared" si="175"/>
-        <v>388.92832476971574</v>
+        <v>381.10055497898475</v>
       </c>
       <c r="CL34" s="55">
         <f t="shared" si="175"/>
-        <v>450.04801973277091</v>
+        <v>438.04514929941092</v>
       </c>
       <c r="CM34" s="55">
         <f t="shared" si="175"/>
-        <v>515.63983977464386</v>
+        <v>500.6256936305461</v>
       </c>
       <c r="CN34" s="55">
         <f t="shared" si="175"/>
-        <v>592.72930222499497</v>
+        <v>574.08478956079932</v>
       </c>
       <c r="CO34" s="55">
         <f t="shared" si="175"/>
-        <v>674.76196241248806</v>
+        <v>654.47582171733745</v>
       </c>
       <c r="CP34" s="55">
         <f t="shared" si="175"/>
-        <v>776.97711136636894</v>
+        <v>754.51798321261822</v>
       </c>
     </row>
     <row r="35" spans="2:146" s="51" customFormat="1" ht="14.25" customHeight="1">
@@ -18757,243 +18757,243 @@
       </c>
       <c r="CG35" s="57">
         <f>CG33-CG34</f>
-        <v>779.52490271875001</v>
+        <v>791.74887642500005</v>
       </c>
       <c r="CH35" s="57">
         <f t="shared" ref="CH35:CP35" si="182">CH33-CH34</f>
-        <v>974.54749582777492</v>
+        <v>1016.5204952194497</v>
       </c>
       <c r="CI35" s="57">
         <f t="shared" si="182"/>
-        <v>1183.5429796532585</v>
+        <v>1248.8478175991615</v>
       </c>
       <c r="CJ35" s="57">
         <f t="shared" si="182"/>
-        <v>1419.183202202352</v>
+        <v>1491.018305337474</v>
       </c>
       <c r="CK35" s="57">
         <f t="shared" si="182"/>
-        <v>1658.0628582287882</v>
+        <v>1736.1247504598196</v>
       </c>
       <c r="CL35" s="57">
         <f t="shared" si="182"/>
-        <v>1918.6257683344445</v>
+        <v>1995.5390134750944</v>
       </c>
       <c r="CM35" s="57">
         <f t="shared" si="182"/>
-        <v>2198.2540537761133</v>
+        <v>2280.6281598724877</v>
       </c>
       <c r="CN35" s="57">
         <f t="shared" si="182"/>
-        <v>2526.8986042223469</v>
+        <v>2615.2751524436417</v>
       </c>
       <c r="CO35" s="57">
         <f t="shared" si="182"/>
-        <v>2876.6167871269226</v>
+        <v>2981.5009656012039</v>
       </c>
       <c r="CP35" s="57">
         <f t="shared" si="182"/>
-        <v>3312.3761063513621</v>
+        <v>3437.2485901908162</v>
       </c>
       <c r="CQ35" s="57">
         <f>CP35*(1+$CP$49)</f>
-        <v>3386.9045687442676</v>
+        <v>3514.5866834701096</v>
       </c>
       <c r="CR35" s="57">
         <f t="shared" ref="CR35:EN35" si="183">CQ35*(1+$CP$49)</f>
-        <v>3463.1099215410136</v>
+        <v>3593.6648838481869</v>
       </c>
       <c r="CS35" s="57">
         <f t="shared" si="183"/>
-        <v>3541.0298947756864</v>
+        <v>3674.5223437347709</v>
       </c>
       <c r="CT35" s="57">
         <f t="shared" si="183"/>
-        <v>3620.7030674081393</v>
+        <v>3757.199096468803</v>
       </c>
       <c r="CU35" s="57">
         <f t="shared" si="183"/>
-        <v>3702.1688864248222</v>
+        <v>3841.7360761393511</v>
       </c>
       <c r="CV35" s="57">
         <f t="shared" si="183"/>
-        <v>3785.4676863693803</v>
+        <v>3928.1751378524864</v>
       </c>
       <c r="CW35" s="57">
         <f t="shared" si="183"/>
-        <v>3870.6407093126913</v>
+        <v>4016.5590784541673</v>
       </c>
       <c r="CX35" s="57">
         <f t="shared" si="183"/>
-        <v>3957.7301252722268</v>
+        <v>4106.9316577193858</v>
       </c>
       <c r="CY35" s="57">
         <f t="shared" si="183"/>
-        <v>4046.7790530908519</v>
+        <v>4199.3376200180719</v>
       </c>
       <c r="CZ35" s="57">
         <f t="shared" si="183"/>
-        <v>4137.8315817853963</v>
+        <v>4293.8227164684786</v>
       </c>
       <c r="DA35" s="57">
         <f t="shared" si="183"/>
-        <v>4230.9327923755673</v>
+        <v>4390.4337275890193</v>
       </c>
       <c r="DB35" s="57">
         <f t="shared" si="183"/>
-        <v>4326.1287802040169</v>
+        <v>4489.2184864597721</v>
       </c>
       <c r="DC35" s="57">
         <f t="shared" si="183"/>
-        <v>4423.4666777586071</v>
+        <v>4590.2259024051164</v>
       </c>
       <c r="DD35" s="57">
         <f t="shared" si="183"/>
-        <v>4522.9946780081755</v>
+        <v>4693.5059852092318</v>
       </c>
       <c r="DE35" s="57">
         <f t="shared" si="183"/>
-        <v>4624.762058263359</v>
+        <v>4799.109869876439</v>
       </c>
       <c r="DF35" s="57">
         <f t="shared" si="183"/>
-        <v>4728.8192045742844</v>
+        <v>4907.0898419486584</v>
       </c>
       <c r="DG35" s="57">
         <f t="shared" si="183"/>
-        <v>4835.2176366772055</v>
+        <v>5017.4993633925033</v>
       </c>
       <c r="DH35" s="57">
         <f t="shared" si="183"/>
-        <v>4944.0100335024426</v>
+        <v>5130.3930990688341</v>
       </c>
       <c r="DI35" s="57">
         <f t="shared" si="183"/>
-        <v>5055.2502592562478</v>
+        <v>5245.8269437978824</v>
       </c>
       <c r="DJ35" s="57">
         <f t="shared" si="183"/>
-        <v>5168.993390089513</v>
+        <v>5363.8580500333346</v>
       </c>
       <c r="DK35" s="57">
         <f t="shared" si="183"/>
-        <v>5285.2957413665272</v>
+        <v>5484.5448561590847</v>
       </c>
       <c r="DL35" s="57">
         <f t="shared" si="183"/>
-        <v>5404.214895547274</v>
+        <v>5607.947115422664</v>
       </c>
       <c r="DM35" s="57">
         <f t="shared" si="183"/>
-        <v>5525.8097306970876</v>
+        <v>5734.1259255196737</v>
       </c>
       <c r="DN35" s="57">
         <f t="shared" si="183"/>
-        <v>5650.1404496377718</v>
+        <v>5863.1437588438666</v>
       </c>
       <c r="DO35" s="57">
         <f t="shared" si="183"/>
-        <v>5777.2686097546211</v>
+        <v>5995.0644934178536</v>
       </c>
       <c r="DP35" s="57">
         <f t="shared" si="183"/>
-        <v>5907.2571534741001</v>
+        <v>6129.9534445197551</v>
       </c>
       <c r="DQ35" s="57">
         <f t="shared" si="183"/>
-        <v>6040.1704394272674</v>
+        <v>6267.8773970214497</v>
       </c>
       <c r="DR35" s="57">
         <f t="shared" si="183"/>
-        <v>6176.074274314381</v>
+        <v>6408.9046384544317</v>
       </c>
       <c r="DS35" s="57">
         <f t="shared" si="183"/>
-        <v>6315.0359454864547</v>
+        <v>6553.1049928196562</v>
       </c>
       <c r="DT35" s="57">
         <f t="shared" si="183"/>
-        <v>6457.1242542598993</v>
+        <v>6700.5498551580986</v>
       </c>
       <c r="DU35" s="57">
         <f t="shared" si="183"/>
-        <v>6602.4095499807472</v>
+        <v>6851.3122268991556</v>
       </c>
       <c r="DV35" s="57">
         <f t="shared" si="183"/>
-        <v>6750.9637648553135</v>
+        <v>7005.4667520043868</v>
       </c>
       <c r="DW35" s="57">
         <f t="shared" si="183"/>
-        <v>6902.8604495645577</v>
+        <v>7163.0897539244852</v>
       </c>
       <c r="DX35" s="57">
         <f t="shared" si="183"/>
-        <v>7058.1748096797601</v>
+        <v>7324.2592733877855</v>
       </c>
       <c r="DY35" s="57">
         <f t="shared" si="183"/>
-        <v>7216.9837428975543</v>
+        <v>7489.0551070390102</v>
       </c>
       <c r="DZ35" s="57">
         <f t="shared" si="183"/>
-        <v>7379.3658771127493</v>
+        <v>7657.5588469473878</v>
       </c>
       <c r="EA35" s="57">
         <f t="shared" si="183"/>
-        <v>7545.4016093477858</v>
+        <v>7829.8539210037034</v>
       </c>
       <c r="EB35" s="57">
         <f t="shared" si="183"/>
-        <v>7715.1731455581103</v>
+        <v>8006.0256342262865</v>
       </c>
       <c r="EC35" s="57">
         <f t="shared" si="183"/>
-        <v>7888.7645413331675</v>
+        <v>8186.161210996378</v>
       </c>
       <c r="ED35" s="57">
         <f t="shared" si="183"/>
-        <v>8066.2617435131633</v>
+        <v>8370.3498382437956</v>
       </c>
       <c r="EE35" s="57">
         <f t="shared" si="183"/>
-        <v>8247.7526327422092</v>
+        <v>8558.6827096042798</v>
       </c>
       <c r="EF35" s="57">
         <f t="shared" si="183"/>
-        <v>8433.327066978909</v>
+        <v>8751.2530705703757</v>
       </c>
       <c r="EG35" s="57">
         <f t="shared" si="183"/>
-        <v>8623.0769259859335</v>
+        <v>8948.1562646582097</v>
       </c>
       <c r="EH35" s="57">
         <f t="shared" si="183"/>
-        <v>8817.0961568206167</v>
+        <v>9149.4897806130193</v>
       </c>
       <c r="EI35" s="57">
         <f t="shared" si="183"/>
-        <v>9015.4808203490811</v>
+        <v>9355.3533006768121</v>
       </c>
       <c r="EJ35" s="57">
         <f t="shared" si="183"/>
-        <v>9218.3291388069356</v>
+        <v>9565.8487499420407</v>
       </c>
       <c r="EK35" s="57">
         <f t="shared" si="183"/>
-        <v>9425.7415444300914</v>
+        <v>9781.0803468157355</v>
       </c>
       <c r="EL35" s="57">
         <f t="shared" si="183"/>
-        <v>9637.820729179768</v>
+        <v>10001.154654619089</v>
       </c>
       <c r="EM35" s="57">
         <f t="shared" si="183"/>
-        <v>9854.6716955863121</v>
+        <v>10226.180634348018</v>
       </c>
       <c r="EN35" s="57">
         <f t="shared" si="183"/>
-        <v>10076.401808737004</v>
+        <v>10456.269698620848</v>
       </c>
       <c r="EO35" s="52"/>
       <c r="EP35" s="52"/>
@@ -20182,10 +20182,10 @@
         <v>0.13696999752045624</v>
       </c>
       <c r="CG40" s="60">
-        <v>0.13300000000000001</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="CH40" s="60">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="CI40" s="60">
         <v>0.127</v>
@@ -20509,34 +20509,34 @@
         <v>0.31881973716836098</v>
       </c>
       <c r="CG41" s="60">
-        <v>0.28599999999999998</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="CH41" s="60">
-        <v>0.28299999999999997</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="CI41" s="60">
-        <v>0.28000000000000003</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="CJ41" s="60">
-        <v>0.27600000000000002</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="CK41" s="60">
-        <v>0.27300000000000002</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="CL41" s="60">
-        <v>0.27</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="CM41" s="60">
-        <v>0.26800000000000002</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="CN41" s="60">
-        <v>0.26600000000000001</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="CO41" s="60">
-        <v>0.26500000000000001</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="CP41" s="60">
-        <v>0.26400000000000001</v>
+        <v>0.26100000000000001</v>
       </c>
     </row>
     <row r="42" spans="2:146" ht="14.25" customHeight="1">
@@ -21169,28 +21169,28 @@
         <v>0.19</v>
       </c>
       <c r="CI43" s="60">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="CJ43" s="60">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="CK43" s="60">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="CL43" s="60">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="CM43" s="60">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="CN43" s="60">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="CO43" s="60">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="CP43" s="60">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="44" spans="2:146" ht="14.25" customHeight="1">
@@ -21606,43 +21606,43 @@
       </c>
       <c r="CG46" s="55">
         <f>CF46-CF64+CG35</f>
-        <v>148.62490271875004</v>
+        <v>160.84887642500007</v>
       </c>
       <c r="CH46" s="55">
         <f t="shared" ref="CH46:CP46" si="208">CG46-CG64+CH35</f>
-        <v>1123.1723985465251</v>
+        <v>1177.3693716444498</v>
       </c>
       <c r="CI46" s="55">
         <f t="shared" si="208"/>
-        <v>2306.7153781997836</v>
+        <v>2426.2171892436113</v>
       </c>
       <c r="CJ46" s="55">
         <f t="shared" si="208"/>
-        <v>3725.8985804021358</v>
+        <v>3917.2354945810853</v>
       </c>
       <c r="CK46" s="55">
         <f t="shared" si="208"/>
-        <v>5383.961438630924</v>
+        <v>5653.3602450409053</v>
       </c>
       <c r="CL46" s="55">
         <f t="shared" si="208"/>
-        <v>7302.5872069653688</v>
+        <v>7648.8992585159995</v>
       </c>
       <c r="CM46" s="55">
         <f t="shared" si="208"/>
-        <v>9500.841260741483</v>
+        <v>9929.5274183884867</v>
       </c>
       <c r="CN46" s="55">
         <f t="shared" si="208"/>
-        <v>12027.739864963831</v>
+        <v>12544.802570832129</v>
       </c>
       <c r="CO46" s="55">
         <f t="shared" si="208"/>
-        <v>14904.356652090753</v>
+        <v>15526.303536433334</v>
       </c>
       <c r="CP46" s="55">
         <f t="shared" si="208"/>
-        <v>18216.732758442115</v>
+        <v>18963.552126624149</v>
       </c>
     </row>
     <row r="47" spans="2:146" ht="14.25" customHeight="1">
@@ -21827,7 +21827,7 @@
         <v>173</v>
       </c>
       <c r="CP48" s="70">
-        <v>0.161</v>
+        <v>0.17499999999999999</v>
       </c>
     </row>
     <row r="49" spans="2:146" ht="14.25" customHeight="1">
@@ -22019,7 +22019,7 @@
       </c>
       <c r="CH50" s="71">
         <f>AVERAGE(CG31)*(1-CG43)</f>
-        <v>679.23482021874997</v>
+        <v>690.24943892500005</v>
       </c>
       <c r="CJ50" s="55">
         <f>SUM(CE46:CE50)-CE59+CE54+CE53+CE51</f>
@@ -22037,7 +22037,7 @@
         <v>176</v>
       </c>
       <c r="CP50" s="70">
-        <v>3.9899999999999998E-2</v>
+        <v>4.1599999999999998E-2</v>
       </c>
     </row>
     <row r="51" spans="2:146" ht="14.25" customHeight="1">
@@ -22126,14 +22126,14 @@
       </c>
       <c r="CH51" s="60">
         <f>CH50/CM50</f>
-        <v>0.15915338587064759</v>
+        <v>0.16173425158746893</v>
       </c>
       <c r="CO51" s="40" t="s">
         <v>1523</v>
       </c>
       <c r="CP51" s="70">
         <f>7.75%-CP50</f>
-        <v>3.7600000000000001E-2</v>
+        <v>3.5900000000000001E-2</v>
       </c>
     </row>
     <row r="52" spans="2:146" ht="14.25" customHeight="1">
@@ -22324,7 +22324,7 @@
       </c>
       <c r="CP53" s="70">
         <f>+CP50+(CP51*CP52)</f>
-        <v>9.5924000000000009E-2</v>
+        <v>9.5091000000000009E-2</v>
       </c>
     </row>
     <row r="54" spans="2:146" ht="14.25" customHeight="1">
@@ -22502,7 +22502,7 @@
       </c>
       <c r="CP55" s="55">
         <f>NPV(CP53,CG35:ED35)</f>
-        <v>27825.72003174917</v>
+        <v>29256.420669272735</v>
       </c>
     </row>
     <row r="56" spans="2:146" ht="14.25" customHeight="1">
@@ -22720,7 +22720,7 @@
       </c>
       <c r="CP57" s="73">
         <f>CP55/CP56</f>
-        <v>71.348000081408131</v>
+        <v>75.016463254545471</v>
       </c>
       <c r="CQ57" s="74"/>
       <c r="CR57" s="52"/>
@@ -22813,7 +22813,7 @@
       </c>
       <c r="CP58" s="73">
         <f>Main!C3</f>
-        <v>58.23</v>
+        <v>67.55</v>
       </c>
       <c r="CQ58" s="75"/>
     </row>
@@ -22906,7 +22906,7 @@
       </c>
       <c r="CP59" s="70">
         <f>CP57/CP58-1</f>
-        <v>0.22527906717170065</v>
+        <v>0.11053239458986641</v>
       </c>
       <c r="CQ59" s="76" t="str">
         <f>IF(CP59&gt;0,"Upside","Downside")</f>
@@ -26616,7 +26616,7 @@
     <ignoredError sqref="CG10:CP10 CC8:CF8 CC9:CF9 CB11:CF11 CC10:CF10 BT22:CF22 CF12 B86:AL87 B85 CC19:CF21 BS37:CF37" evalError="1"/>
     <ignoredError sqref="BS84:CF85" evalError="1" formula="1"/>
     <ignoredError sqref="C83:BH83 AC84:BH84" formula="1"/>
-    <ignoredError sqref="AP71:BH78 CB26:CF26 BS27:CF35 BS26:CA26 BS81:CF82" formulaRange="1"/>
+    <ignoredError sqref="AP71:BH78 CB26:CF26 BS27:CF35 BS26:CA26 BS81:CF82 BI71:BI76" formulaRange="1"/>
     <ignoredError sqref="BS36" evalError="1" formulaRange="1"/>
     <ignoredError sqref="BT36:CF36" evalError="1" formula="1" formulaRange="1"/>
   </ignoredErrors>
